--- a/Workbook1.xlsx
+++ b/Workbook1.xlsx
@@ -1375,6 +1375,15 @@
       <c r="A6" t="s">
         <v>14</v>
       </c>
+      <c r="B6">
+        <v>0.904941</v>
+      </c>
+      <c r="C6">
+        <v>0.754298</v>
+      </c>
+      <c r="D6">
+        <v>0.656571</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">

--- a/Workbook1.xlsx
+++ b/Workbook1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>model</t>
   </si>
@@ -83,9 +83,6 @@
     <t>kitti_8n_int8_ptq</t>
   </si>
   <si>
-    <t>kitti_8n_f16_qat</t>
-  </si>
-  <si>
     <t>kitti_8n_int8_qat</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>float32: 42,275, int32: 5,515, int64: 25, int8: 2,803,636</t>
   </si>
   <si>
-    <t>milad_voc_8n_f16_qat</t>
-  </si>
-  <si>
     <t>milad_voc_8n_int8_qat</t>
   </si>
   <si>
@@ -120,9 +114,6 @@
   </si>
   <si>
     <t>voc_8n_int8_ptq</t>
-  </si>
-  <si>
-    <t>voc_8n_f16_qat</t>
   </si>
   <si>
     <t>voc_8n_int8_qat</t>
@@ -1273,7 +1264,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="22.5234375" customWidth="1"/>
@@ -1385,6 +1376,18 @@
         <v>0.656571</v>
       </c>
     </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>0.898171</v>
+      </c>
+      <c r="C7">
+        <v>0.752284</v>
+      </c>
+      <c r="D7">
+        <f>0.651648</f>
+        <v>0.651648</v>
+      </c>
+    </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>15</v>
@@ -1435,73 +1438,103 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>19</v>
+      </c>
+      <c r="B13">
+        <v>0.804999</v>
+      </c>
+      <c r="C13">
+        <v>0.655185</v>
+      </c>
+      <c r="D13">
+        <v>0.590294</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2814081</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
-        <v>0.804999</v>
+        <v>0.805077</v>
       </c>
       <c r="C14">
-        <v>0.655185</v>
+        <v>0.655366</v>
       </c>
       <c r="D14">
-        <v>0.590294</v>
-      </c>
-      <c r="E14" s="1">
-        <v>2814081</v>
+        <v>0.590312</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
-        <v>0.805077</v>
+        <v>0.786007</v>
       </c>
       <c r="C15">
-        <v>0.655366</v>
+        <v>0.62437</v>
       </c>
       <c r="D15">
-        <v>0.590312</v>
+        <v>0.559133</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
-        <v>0.786007</v>
+        <v>0.821769</v>
       </c>
       <c r="C16">
-        <v>0.62437</v>
+        <v>0.674819</v>
       </c>
       <c r="D16">
-        <v>0.559133</v>
-      </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>26</v>
+        <v>0.605649</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18">
+        <v>0.82505</v>
+      </c>
+      <c r="C18">
+        <v>0.687812</v>
+      </c>
+      <c r="D18">
+        <v>0.621331</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3014748</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
         <v>27</v>
+      </c>
+      <c r="B19">
+        <v>0.825345</v>
+      </c>
+      <c r="C19">
+        <v>0.687515</v>
+      </c>
+      <c r="D19">
+        <v>0.621537</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1509,54 +1542,18 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0.82505</v>
+        <v>0.809601</v>
       </c>
       <c r="C20">
-        <v>0.687812</v>
+        <v>0.661288</v>
       </c>
       <c r="D20">
-        <v>0.621331</v>
-      </c>
-      <c r="E20" s="1">
-        <v>3014748</v>
+        <v>0.596115</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>29</v>
-      </c>
-      <c r="B21">
-        <v>0.825345</v>
-      </c>
-      <c r="C21">
-        <v>0.687515</v>
-      </c>
-      <c r="D21">
-        <v>0.621537</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22">
-        <v>0.809601</v>
-      </c>
-      <c r="C22">
-        <v>0.661288</v>
-      </c>
-      <c r="D22">
-        <v>0.596115</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Workbook1.xlsx
+++ b/Workbook1.xlsx
@@ -1367,23 +1367,12 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0.904941</v>
+        <v>0.898171</v>
       </c>
       <c r="C6">
-        <v>0.754298</v>
+        <v>0.752284</v>
       </c>
       <c r="D6">
-        <v>0.656571</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7">
-        <v>0.898171</v>
-      </c>
-      <c r="C7">
-        <v>0.752284</v>
-      </c>
-      <c r="D7">
         <f>0.651648</f>
         <v>0.651648</v>
       </c>

--- a/Workbook1.xlsx
+++ b/Workbook1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>model</t>
   </si>
@@ -53,6 +53,9 @@
     <t>float32: 1,465,457, int64: 25</t>
   </si>
   <si>
+    <t>compressed</t>
+  </si>
+  <si>
     <t>milad_kitti_8n_f16_ptq</t>
   </si>
   <si>
@@ -74,9 +77,15 @@
     <t>milad_kitti_8n_int8_qat</t>
   </si>
   <si>
+    <t>float32: 17,627, int8: 1,418,020</t>
+  </si>
+  <si>
     <t>kitti_8n_f32</t>
   </si>
   <si>
+    <t>origin</t>
+  </si>
+  <si>
     <t>kitti_8n_f16_ptq</t>
   </si>
   <si>
@@ -105,6 +114,9 @@
   </si>
   <si>
     <t>milad_voc_8n_int8_qat</t>
+  </si>
+  <si>
+    <t>float32: 16,564, int8: 2,803,429</t>
   </si>
   <si>
     <t>voc_8n_f32</t>
@@ -129,10 +141,17 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -282,12 +301,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -602,55 +627,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -665,78 +687,96 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1264,14 +1304,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.5234375" customWidth="1"/>
     <col min="2" max="5" width="9.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1291,7 +1331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1304,16 +1344,19 @@
       <c r="D2">
         <v>0.674389</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="3">
         <v>1428652</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0.890854</v>
@@ -1324,30 +1367,36 @@
       <c r="D3">
         <v>0.675118</v>
       </c>
+      <c r="E3" s="3">
+        <v>1428652</v>
+      </c>
       <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1">
         <v>0.874527</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>0.685279</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>0.612294</v>
       </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="E4" s="4">
+        <v>1428652</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>0.909407</v>
@@ -1358,28 +1407,37 @@
       <c r="D5">
         <v>0.668009</v>
       </c>
+      <c r="E5" s="3">
+        <v>1428652</v>
+      </c>
       <c r="F5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6">
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:10">
+      <c r="A6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2">
         <v>0.898171</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>0.752284</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <f>0.651648</f>
         <v>0.651648</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="E6" s="6">
+        <v>1435647</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>0.9054</v>
@@ -1390,13 +1448,16 @@
       <c r="D8">
         <v>0.6733</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="3">
         <v>3012408</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>0.9051</v>
@@ -1408,28 +1469,37 @@
         <v>0.674</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
+    <row r="10" s="1" customFormat="1" spans="1:10">
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.8832</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>0.7193</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>0.6155</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+    <row r="11" s="2" customFormat="1" spans="1:10">
+      <c r="A11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.891497</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.740264</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.64706</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>0.804999</v>
@@ -1440,16 +1510,16 @@
       <c r="D13">
         <v>0.590294</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="3">
         <v>2814081</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>0.805077</v>
@@ -1460,44 +1530,56 @@
       <c r="D14">
         <v>0.590312</v>
       </c>
+      <c r="E14" s="3">
+        <v>2851451</v>
+      </c>
       <c r="F14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1">
         <v>0.786007</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>0.62437</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>0.559133</v>
       </c>
-      <c r="F15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16">
+      <c r="E15" s="4">
+        <v>2851451</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:10">
+      <c r="A16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="1">
         <v>0.821769</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>0.674819</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>0.605649</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2819993</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>0.82505</v>
@@ -1508,13 +1590,13 @@
       <c r="D18">
         <v>0.621331</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="3">
         <v>3014748</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B19">
         <v>0.825345</v>
@@ -1526,23 +1608,32 @@
         <v>0.621537</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20">
+    <row r="20" s="1" customFormat="1" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="1">
         <v>0.809601</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>0.661288</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>0.596115</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>29</v>
+    <row r="21" s="1" customFormat="1" spans="1:5">
+      <c r="A21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0.813138</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.667647</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.601649</v>
       </c>
     </row>
   </sheetData>
